--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30619d2d71c64cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3d3f3c2ca34435b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3d3f3c2ca34435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb278726402d04eee"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb278726402d04eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0903c1b19124459f"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0903c1b19124459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62ad0c99025f4767"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62ad0c99025f4767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02970d4a2f034ab8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02970d4a2f034ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d8200c02ae74ab6"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d8200c02ae74ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ffd8785873d442b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ffd8785873d442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96072fd6bec84aa6"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96072fd6bec84aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d81066c64ec424f"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d81066c64ec424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra070c68dc2544cc6"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra070c68dc2544cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3516b7fa98843d2"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3516b7fa98843d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2417c0cad393404b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2417c0cad393404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf050a83f45f54ab5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf050a83f45f54ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1aef377c8f7e43fd"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1aef377c8f7e43fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35551c474e034807"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>
